--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.46117146018567</v>
+        <v>3.812440362280172</v>
       </c>
       <c r="D2" t="n">
-        <v>6.275534260198327</v>
+        <v>1.019774317282228</v>
       </c>
       <c r="E2" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F2" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.08269871025984</v>
+        <v>4.400938540417224</v>
       </c>
       <c r="D3" t="n">
-        <v>15.60228652681396</v>
+        <v>2.535371560607268</v>
       </c>
       <c r="E3" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F3" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.25902829690808</v>
+        <v>7.842092098247563</v>
       </c>
       <c r="D4" t="n">
-        <v>42.84546512794765</v>
+        <v>6.962388083291493</v>
       </c>
       <c r="E4" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F4" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.45749684879841</v>
+        <v>2.349343237929742</v>
       </c>
       <c r="D5" t="n">
-        <v>9.150574966756027</v>
+        <v>1.486968432097854</v>
       </c>
       <c r="E5" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F5" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.4902468832917</v>
+        <v>6.579665118534902</v>
       </c>
       <c r="D6" t="n">
-        <v>1.157730242521615</v>
+        <v>0.1881311644097625</v>
       </c>
       <c r="E6" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F6" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.24297422212509</v>
+        <v>2.476983311095328</v>
       </c>
       <c r="D7" t="n">
-        <v>7.394816641129182</v>
+        <v>1.201657704183492</v>
       </c>
       <c r="E7" t="n">
-        <v>12.47566600499611</v>
+        <v>2.027295725811868</v>
       </c>
       <c r="F7" t="n">
-        <v>13.69885710351257</v>
+        <v>2.226064279320793</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
